--- a/examples/answer_key.xlsx
+++ b/examples/answer_key.xlsx
@@ -9,14 +9,22 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Истина" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Истина'!$A$1:$W$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Истина'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,13 +66,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -455,9 +482,10 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="88" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Файл</t>
@@ -500,7 +528,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Полоса, нм</t>
+          <t>Полоса, нм (FWHM)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -510,12 +538,12 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A, эВ</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>E0, эВ</t>
+          <t>E₀, эВ</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -525,12 +553,12 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Eg, эВ</t>
+          <t>E_g, эВ</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>A_uv</t>
+          <t>A_uv, эВ²</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -540,36 +568,41 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>n(450)</t>
+          <t>n(450 нм)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>n(550)</t>
+          <t>n(550 нм)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n(650)</t>
+          <t>n(650 нм)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>n(750)</t>
+          <t>n(750 нм)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>k(450)</t>
+          <t>k(450 нм)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>k(550)</t>
+          <t>k(550 нм)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>E_uv, эВ</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>01_TiO2_on_BK7_65deg.xlsx</t>
@@ -580,16 +613,16 @@
           <t>TiO₂ на BK7, 65°</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>1017.3</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>2.2</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -597,53 +630,56 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="5" t="n">
         <v>65.02</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="5" t="n">
         <v>261.97</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="5" t="n">
         <v>4.04</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="5" t="n">
         <v>1.82</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="5" t="n">
         <v>3.37</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="5" t="n">
         <v>131.46</v>
       </c>
-      <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2" t="n">
+      <c r="P2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="6" t="n">
         <v>2.4249</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="6" t="n">
         <v>2.3248</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="6" t="n">
         <v>2.2784</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" s="6" t="n">
         <v>2.2522</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>0</v>
+      <c r="U2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>11</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>02_Ta2O5_on_fused_silica_60deg.xlsx</t>
@@ -654,16 +690,16 @@
           <t>Ta₂O₅ на плавленом кварце, 60°</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>862.4</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="D3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -671,53 +707,56 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="5" t="n">
         <v>59.98</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="5" t="n">
         <v>-0.04</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="5" t="n">
         <v>311.7</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="5" t="n">
         <v>5.25</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="5" t="n">
         <v>4.15</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="5" t="n">
         <v>11.33</v>
       </c>
-      <c r="P3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2" t="n">
+      <c r="P3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="6" t="n">
         <v>2.1832</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="6" t="n">
         <v>2.1285</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="6" t="n">
         <v>2.1004</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="T3" s="6" t="n">
         <v>2.0838</v>
       </c>
-      <c r="U3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>0</v>
+      <c r="U3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>03_Nb2O5_on_BK7_60deg.xlsx</t>
@@ -728,16 +767,16 @@
           <t>Nb₂O₅ на BK7, 60°</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>1188</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,53 +784,56 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="5" t="n">
         <v>60.03</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="5" t="n">
         <v>317.99</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="5" t="n">
         <v>4.72</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="5" t="n">
         <v>2.25</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="5" t="n">
         <v>3.78</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="5" t="n">
         <v>66.31</v>
       </c>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
+      <c r="P4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6" t="n">
         <v>2.4002</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="6" t="n">
         <v>2.3235</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="6" t="n">
         <v>2.2854</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T4" s="6" t="n">
         <v>2.2632</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>0</v>
+      <c r="U4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>11</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>04_Si3N4_on_Si_70deg.xlsx</t>
@@ -802,16 +844,16 @@
           <t>Si₃N₄ на кремнии, 70°</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>612.5</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -819,53 +861,56 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="5" t="n">
         <v>70.01000000000001</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="5" t="n">
         <v>161.21</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="5" t="n">
         <v>7.1</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="5" t="n">
         <v>101.24</v>
       </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
+      <c r="P5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6" t="n">
         <v>2.0077</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="6" t="n">
         <v>1.9807</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="6" t="n">
         <v>1.9662</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="T5" s="6" t="n">
         <v>1.9574</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
+      <c r="U5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>13</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>05_HfO2_on_Si_65deg.xlsx</t>
@@ -876,16 +921,16 @@
           <t>HfO₂ на кремнии, 65°</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>933</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -893,53 +938,56 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="5" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="5" t="n">
         <v>391.02</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="5" t="n">
         <v>6.15</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="5" t="n">
         <v>2.85</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="5" t="n">
         <v>5.16</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="5" t="n">
         <v>17.49</v>
       </c>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2" t="n">
+      <c r="P6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6" t="n">
         <v>2.0024</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="6" t="n">
         <v>1.9724</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="6" t="n">
         <v>1.9563</v>
       </c>
-      <c r="T6" s="2" t="n">
+      <c r="T6" s="6" t="n">
         <v>1.9466</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>0</v>
+      <c r="U6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>13</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>06_SiNx_on_fused_silica_65deg.xlsx</t>
@@ -950,16 +998,16 @@
           <t>SiNₓ:H (обогащённый Si) на плавленом кварце, 65°</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>712.6</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n">
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -967,53 +1015,56 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="5" t="n">
         <v>65.02</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="5" t="n">
         <v>53.6</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="5" t="n">
         <v>7.42</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="5" t="n">
         <v>2.14</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="5" t="n">
         <v>76.97</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="P7" s="6" t="n">
         <v>1.0222</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" s="6" t="n">
         <v>2.2725</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="6" t="n">
         <v>2.2081</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="S7" s="6" t="n">
         <v>2.1747</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="T7" s="6" t="n">
         <v>2.1566</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" s="7" t="n">
         <v>0.01905</v>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" s="7" t="n">
         <v>0.00177</v>
       </c>
+      <c r="W7" s="3" t="n">
+        <v>13</v>
+      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>07_WO3_on_BK7_60deg.xlsx</t>
@@ -1024,16 +1075,16 @@
           <t>WO₃ на BK7, 60° (350–800 нм)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>838.2</v>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1041,53 +1092,56 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="5" t="n">
         <v>60.02</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="5" t="n">
         <v>58.36</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" s="5" t="n">
         <v>4.45</v>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="M8" s="5" t="n">
         <v>1.24</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="5" t="n">
         <v>3.23</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O8" s="5" t="n">
         <v>304.79</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P8" s="6" t="n">
         <v>0.1575</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="Q8" s="6" t="n">
         <v>2.0713</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R8" s="6" t="n">
         <v>2.0176</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="S8" s="6" t="n">
         <v>1.9925</v>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="T8" s="6" t="n">
         <v>1.9784</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U8" s="7" t="n">
         <v>0.00115</v>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="V8" s="7" t="n">
         <v>0.00047</v>
       </c>
+      <c r="W8" s="3" t="n">
+        <v>13</v>
+      </c>
     </row>
-    <row r="9">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>08_CeO2_on_Si_65deg.xlsx</t>
@@ -1098,16 +1152,16 @@
           <t>CeO₂ на кремнии, 65°</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>887.5</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1115,53 +1169,56 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="5" t="n">
         <v>65.03</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="5" t="n">
         <v>66.89</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="L9" s="5" t="n">
         <v>3.94</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="M9" s="5" t="n">
         <v>0.91</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" s="5" t="n">
         <v>2.79</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="O9" s="5" t="n">
         <v>406.29</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="P9" s="6" t="n">
         <v>0.0667</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="Q9" s="6" t="n">
         <v>2.4354</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="R9" s="6" t="n">
         <v>2.3186</v>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="S9" s="6" t="n">
         <v>2.2719</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="T9" s="6" t="n">
         <v>2.247</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="U9" s="7" t="n">
         <v>0.00062</v>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="V9" s="7" t="n">
         <v>0.00022</v>
       </c>
+      <c r="W9" s="3" t="n">
+        <v>13</v>
+      </c>
     </row>
-    <row r="10">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>09_ZrO2_on_fused_silica_1mm_backside_65deg.xlsx</t>
@@ -1172,16 +1229,16 @@
           <t>ZrO₂ на плавленом кварце 1 мм с задней стороной, 65°</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="3" t="n">
         <v>780.4</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="4" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1189,65 +1246,72 @@
           <t>0.960 (0.95 ± 0.02)</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="5" t="n">
         <v>65.01000000000001</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="5" t="n">
         <v>-0.03</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="5" t="n">
         <v>455.73</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" s="5" t="n">
         <v>5.98</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" s="5" t="n">
         <v>3.04</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" s="5" t="n">
         <v>4.96</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="O10" s="5" t="n">
         <v>29.6</v>
       </c>
-      <c r="P10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
+      <c r="P10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6" t="n">
         <v>2.2129</v>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="R10" s="6" t="n">
         <v>2.1761</v>
       </c>
-      <c r="S10" s="2" t="n">
+      <c r="S10" s="6" t="n">
         <v>2.1564</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="T10" s="6" t="n">
         <v>2.1446</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0</v>
+      <c r="U10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>13</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Дисперсия каждой плёнки отличается от справочной (силы осцилляторов, E0, C, Eg), как у реального образца; угол отличается от номинального на 0.01–0.03°; дрейф и шум добавлены. Поглощение задаётся хвостом ниже края (второй осциллятор Тауца–Лоренца с теми же E0, C, порог E_t = 1.2 эВ, сила A_k); k(450), k(550) — полный k плёнки (край материала + хвост); у образцов 01–05 хвоста нет. Задняя сторона подложки (образец 09): пучки, отражённые задней гранью плоскопараллельной подложки, складываются с передним некогерентно; доля собранного света задана из независимого измерения и не фитируется.</t>
+          <t>Дисперсия каждой плёнки отличается от справочной (силы осцилляторов, E0, C, Eg), как у реального образца; угол отличается от номинального на 0.01–0.03°; дрейф и шум добавлены. Это параметры синтетических учебных спектров, не результаты измерений. Поглощение задаётся хвостом ниже края (второй осциллятор Тауца–Лоренца с теми же E0, C, порог E_t = 1.2 эВ, сила A_k); k(450 нм), k(550 нм) — полный k плёнки (край материала + хвост); у образцов 01–05 и 09 дополнительного хвоста нет. Задняя сторона подложки (образец 09): пучки, отражённые задней гранью плоскопараллельной подложки, складываются с передним некогерентно; доля собранного света задана из независимого измерения и не фитируется.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W10"/>
+  <mergeCells count="1">
+    <mergeCell ref="B12:I12"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>